--- a/output/2026-10-05_05_Malesia_Terengganu_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-05_05_Malesia_Terengganu_ATEX_Equipment_Services.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Stocking distributor specializzato in Equipment for Explosive Atmospheres (Eaton Crouse-Hinds, CEAG, Thuba, WINNEX, Mennekes, Fluke, Emerson/Rosemount). ISO 9001:2015 (TUV SUD). Confermato via WebFetch sito ufficiale.</t>
+          <t>Stocking distributor specializzato in Equipment for Explosive Atmospheres (Eaton Crouse-Hinds, CEAG, Thuba, WINNEX, Mennekes, Fluke, Emerson/Rosemount). ISO 9001:2015 (TUV SUD). Confermato via WebFetch sito ufficiale. [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore/rappresentante dal 2004 di illuminazione antideflagrante ed equipaggiamento elettrico per aree pericolose, conforme IEC/CENELEC/CSA/UL/FM/ATEX/IECEx. Confermato via WebFetch sito ufficiale.</t>
+          <t>Distributore/rappresentante dal 2004 di illuminazione antideflagrante ed equipaggiamento elettrico per aree pericolose, conforme IEC/CENELEC/CSA/UL/FM/ATEX/IECEx. Confermato via WebFetch sito ufficiale. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,7 +558,6 @@
           <t>See Kwong Electric (KL) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Puchong, Selangor (copertura Malaysia, settore oil&amp;gas)</t>
@@ -569,11 +568,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dal 1982, rappresentante/importatore/distributore/stockista di prodotti explosion-proof e sicurezza elettrica (cable gland, fusibili industriali, plug &amp; socket, illuminazione Ex) certificati ATEX/IECEx/IEC/CSA. Sito ufficiale non identificato con certezza; confermato solo via WebSearch (maukerja.my, sgpgrid.com).</t>
+          <t>Dal 1982, rappresentante/importatore/distributore/stockista di prodotti explosion-proof e sicurezza elettrica (cable gland, fusibili industriali, plug &amp; socket, illuminazione Ex) certificati ATEX/IECEx/IEC/CSA. Sito ufficiale non identificato con certezza; confermato solo via WebSearch (maukerja.my, sgpgrid.com). [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
